--- a/xls/square_16_quad4_19.xlsx
+++ b/xls/square_16_quad4_19.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17">
+        <v>400</v>
+      </c>
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17">
+        <v>289</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17">
+        <v>324</v>
+      </c>
+      <c r="G17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17">
+        <v>867</v>
+      </c>
+      <c r="I17">
+        <v>0.5498630715318142</v>
+      </c>
+      <c r="J17">
+        <v>-0.809976568648949</v>
+      </c>
+      <c r="K17">
+        <v>1.6328754968595216</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18">
+        <v>400</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18">
+        <v>289</v>
+      </c>
+      <c r="E18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18">
+        <v>361</v>
+      </c>
+      <c r="G18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18">
+        <v>972</v>
+      </c>
+      <c r="I18">
+        <v>-0.9584058060258692</v>
+      </c>
+      <c r="J18">
+        <v>-1.5516046122119127</v>
+      </c>
+      <c r="K18">
+        <v>1.5199101018548724</v>
+      </c>
+    </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
         <v>11</v>
@@ -482,13 +552,13 @@
         <v>1083</v>
       </c>
       <c r="I19">
-        <v>-1.48282620920877</v>
+        <v>-1.4290004784007746</v>
       </c>
       <c r="J19">
-        <v>-1.8817070481233993</v>
+        <v>-1.5449802577297311</v>
       </c>
       <c r="K19">
-        <v>0.8512789518900636</v>
+        <v>1.3368356089806492</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -517,13 +587,13 @@
         <v>1200</v>
       </c>
       <c r="I20">
-        <v>-1.8875423778295262</v>
+        <v>-1.4311223454273163</v>
       </c>
       <c r="J20">
-        <v>-1.8748334234169524</v>
+        <v>-1.5289452346362473</v>
       </c>
       <c r="K20">
-        <v>0.8418978979155509</v>
+        <v>1.720809456102427</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -552,13 +622,13 @@
         <v>1323</v>
       </c>
       <c r="I21">
-        <v>-1.8288137513816272</v>
+        <v>-1.3081236403100602</v>
       </c>
       <c r="J21">
-        <v>-1.8016914429346784</v>
+        <v>-1.4018114046178713</v>
       </c>
       <c r="K21">
-        <v>1.568125312953123</v>
+        <v>3.4724048614470946</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -587,13 +657,13 @@
         <v>1452</v>
       </c>
       <c r="I22">
-        <v>-1.793222907009758</v>
+        <v>-1.4932720418818313</v>
       </c>
       <c r="J22">
-        <v>-1.6577059081388692</v>
+        <v>-1.1402911645523406</v>
       </c>
       <c r="K22">
-        <v>2.086998188716596</v>
+        <v>4.626981664037853</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -622,13 +692,13 @@
         <v>1587</v>
       </c>
       <c r="I23">
-        <v>-1.6112010535130459</v>
+        <v>-0.7206670174757033</v>
       </c>
       <c r="J23">
-        <v>-1.5806189070402281</v>
+        <v>-0.6500566835355209</v>
       </c>
       <c r="K23">
-        <v>2.5254287159110462</v>
+        <v>4.843198012410341</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -657,13 +727,13 @@
         <v>1728</v>
       </c>
       <c r="I24">
-        <v>-0.5417631061137677</v>
+        <v>-0.017436850258288287</v>
       </c>
       <c r="J24">
-        <v>-0.32961742292610363</v>
+        <v>-0.01438765489261213</v>
       </c>
       <c r="K24">
-        <v>3.476372633058765</v>
+        <v>4.410445884371697</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -692,13 +762,13 @@
         <v>1875</v>
       </c>
       <c r="I25">
-        <v>-0.024636963281948282</v>
+        <v>-0.00020297314409921093</v>
       </c>
       <c r="J25">
-        <v>-0.016850322669060162</v>
+        <v>-0.00015421762110959662</v>
       </c>
       <c r="K25">
-        <v>3.3899355003490936</v>
+        <v>3.465390580807745</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -727,13 +797,13 @@
         <v>2028</v>
       </c>
       <c r="I26">
-        <v>-0.012852681432478516</v>
+        <v>-7.095779250694002e-5</v>
       </c>
       <c r="J26">
-        <v>-0.011441978677757364</v>
+        <v>-6.340470990800561e-5</v>
       </c>
       <c r="K26">
-        <v>3.437523191387187</v>
+        <v>3.295833165553471</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -762,13 +832,13 @@
         <v>2187</v>
       </c>
       <c r="I27">
-        <v>-0.002436032528405407</v>
+        <v>-5.045997172154744e-5</v>
       </c>
       <c r="J27">
-        <v>-0.0020726234729681993</v>
+        <v>-4.609035903344089e-5</v>
       </c>
       <c r="K27">
-        <v>3.0798642681790724</v>
+        <v>3.2645850980202313</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -797,13 +867,13 @@
         <v>2352</v>
       </c>
       <c r="I28">
-        <v>-0.001821794919818971</v>
+        <v>-1.9818974264446312e-5</v>
       </c>
       <c r="J28">
-        <v>-0.00175409178281302</v>
+        <v>-1.9191261798513867e-5</v>
       </c>
       <c r="K28">
-        <v>3.071423863145049</v>
+        <v>3.06501460424849</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -832,13 +902,13 @@
         <v>2523</v>
       </c>
       <c r="I29">
-        <v>-0.0003264438282891213</v>
+        <v>-3.149749734250269e-6</v>
       </c>
       <c r="J29">
-        <v>-0.0003094666671555314</v>
+        <v>-3.0325354021000757e-6</v>
       </c>
       <c r="K29">
-        <v>2.7241407928097763</v>
+        <v>2.677494397434375</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -867,13 +937,13 @@
         <v>2700</v>
       </c>
       <c r="I30">
-        <v>-0.0004364421580474319</v>
+        <v>-3.685575010032659e-6</v>
       </c>
       <c r="J30">
-        <v>-0.0004318493655103899</v>
+        <v>-3.596192523781525e-6</v>
       </c>
       <c r="K30">
-        <v>2.7929313072128217</v>
+        <v>2.7048445606644633</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -902,13 +972,13 @@
         <v>2883</v>
       </c>
       <c r="I31">
-        <v>-5.988863015142349e-5</v>
+        <v>-8.346865149815776e-7</v>
       </c>
       <c r="J31">
-        <v>-6.269487508411814e-5</v>
+        <v>-8.206889194354789e-7</v>
       </c>
       <c r="K31">
-        <v>2.3904365857966656</v>
+        <v>2.4101093175001145</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -937,13 +1007,13 @@
         <v>3072</v>
       </c>
       <c r="I32">
-        <v>-4.4443859444951304e-5</v>
+        <v>-6.637645236229676e-7</v>
       </c>
       <c r="J32">
-        <v>-3.797878285165041e-5</v>
+        <v>-5.750003634902366e-7</v>
       </c>
       <c r="K32">
-        <v>2.2452132440107975</v>
+        <v>2.3091206541729203</v>
       </c>
     </row>
   </sheetData>
